--- a/data/demo_tracker.xlsx
+++ b/data/demo_tracker.xlsx
@@ -348,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="184">
   <si>
     <t xml:space="preserve">DEMO DATA: based on a real shipment, with each bag's amounts randomly scaled (up to ±15%) and identifying details removed for the founder's privacy.</t>
   </si>
@@ -689,12 +689,6 @@
     <t xml:space="preserve">Silver</t>
   </si>
   <si>
-    <t xml:space="preserve">Listed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original sheet showed a sale result while still in stock; treated as unsold. Purchase date had day and month swapped in the original sheet; corrected. Lot total price not recorded yet.</t>
-  </si>
-  <si>
     <t xml:space="preserve">DEMO-010</t>
   </si>
   <si>
@@ -717,6 +711,9 @@
   </si>
   <si>
     <t xml:space="preserve">Black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform authenticated</t>
   </si>
   <si>
     <t xml:space="preserve">Supplier B</t>
@@ -743,10 +740,31 @@
     <t xml:space="preserve">Canvas/leather</t>
   </si>
   <si>
+    <t xml:space="preserve">Listed</t>
+  </si>
+  <si>
     <t xml:space="preserve">DEMO-014</t>
   </si>
   <si>
     <t xml:space="preserve">Chanel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sold privately to a personal contact, not through a platform. Purchase date had day and month swapped in the original sheet; corrected. Lot total price not recorded yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEMO-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ostrich leather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added in the founder's updated sheet.</t>
   </si>
   <si>
     <t xml:space="preserve">Business summary</t>
@@ -824,9 +842,6 @@
     <t xml:space="preserve">Burberry</t>
   </si>
   <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
     <t xml:space="preserve">By sales channel</t>
   </si>
   <si>
@@ -843,9 +858,6 @@
   </si>
   <si>
     <t xml:space="preserve">New with tags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform authenticated</t>
   </si>
   <si>
     <t xml:space="preserve">In stock, not listed</t>
@@ -1900,7 +1912,7 @@
         <v>46215</v>
       </c>
       <c r="P3" s="16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>77</v>
@@ -1910,10 +1922,10 @@
       </c>
       <c r="S3" s="18" t="n">
         <f aca="false">IF(OR(P3="",R3=""),"",P3*R3)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" s="14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U3" s="14" t="n">
         <v>0</v>
@@ -1926,14 +1938,14 @@
       </c>
       <c r="X3" s="18" t="n">
         <f aca="false">IF(S3="","",S3+N(T3)+N(U3)+N(V3)+N(W3))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>78</v>
       </c>
       <c r="Z3" s="15"/>
       <c r="AA3" s="14" t="n">
-        <v>344</v>
+        <v>390</v>
       </c>
       <c r="AB3" s="19"/>
       <c r="AC3" s="4" t="s">
@@ -1941,10 +1953,10 @@
       </c>
       <c r="AD3" s="15"/>
       <c r="AE3" s="14" t="n">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="AF3" s="14" t="n">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="AG3" s="14"/>
       <c r="AH3" s="18" t="n">
@@ -1953,15 +1965,15 @@
       </c>
       <c r="AI3" s="18" t="n">
         <f aca="false">IF(AND(AC3="Sold",AF3&lt;&gt;"",X3&lt;&gt;""),AF3-N(AG3)-X3,"")</f>
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="AJ3" s="20" t="n">
         <f aca="false">IF(AND(AI3&lt;&gt;"",N(AE3)&gt;0),AI3/AE3,"")</f>
-        <v>0.923636363636364</v>
+        <v>0.926282051282051</v>
       </c>
       <c r="AK3" s="20" t="n">
         <f aca="false">IF(AND(AI3&lt;&gt;"",N(X3)&gt;0),AI3/X3,"")</f>
-        <v>12.0952380952381</v>
+        <v>12.5652173913043</v>
       </c>
       <c r="AL3" s="21" t="str">
         <f aca="false">IF(AND(AC3="Sold",AD3&lt;&gt;"",Z3&lt;&gt;""),AD3-Z3,"")</f>
@@ -1969,7 +1981,7 @@
       </c>
       <c r="AM3" s="20" t="n">
         <f aca="false">IF(AND(AC3="Sold",N(AA3)&gt;0,AE3&lt;&gt;""),1-AE3/AA3,"")</f>
-        <v>0.200581395348837</v>
+        <v>0.2</v>
       </c>
       <c r="AN3" s="21" t="str">
         <f aca="true">IF(AND(AC3&lt;&gt;"Sold",AC3&lt;&gt;"",Z3&lt;&gt;""),TODAY()-Z3,"")</f>
@@ -2017,7 +2029,7 @@
         <v>46215</v>
       </c>
       <c r="P4" s="16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q4" s="4" t="s">
         <v>77</v>
@@ -2027,7 +2039,7 @@
       </c>
       <c r="S4" s="18" t="n">
         <f aca="false">IF(OR(P4="",R4=""),"",P4*R4)</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="T4" s="14" t="n">
         <v>12</v>
@@ -2043,14 +2055,14 @@
       </c>
       <c r="X4" s="18" t="n">
         <f aca="false">IF(S4="","",S4+N(T4)+N(U4)+N(V4)+N(W4))</f>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y4" s="4" t="s">
         <v>78</v>
       </c>
       <c r="Z4" s="15"/>
       <c r="AA4" s="14" t="n">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="AB4" s="19"/>
       <c r="AC4" s="4" t="s">
@@ -2058,10 +2070,10 @@
       </c>
       <c r="AD4" s="15"/>
       <c r="AE4" s="14" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="AF4" s="14" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="AG4" s="14"/>
       <c r="AH4" s="18" t="n">
@@ -2070,15 +2082,15 @@
       </c>
       <c r="AI4" s="18" t="n">
         <f aca="false">IF(AND(AC4="Sold",AF4&lt;&gt;"",X4&lt;&gt;""),AF4-N(AG4)-X4,"")</f>
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="AJ4" s="20" t="n">
         <f aca="false">IF(AND(AI4&lt;&gt;"",N(AE4)&gt;0),AI4/AE4,"")</f>
-        <v>0.596491228070175</v>
+        <v>0.584905660377359</v>
       </c>
       <c r="AK4" s="20" t="n">
         <f aca="false">IF(AND(AI4&lt;&gt;"",N(X4)&gt;0),AI4/X4,"")</f>
-        <v>1.47826086956522</v>
+        <v>1.40909090909091</v>
       </c>
       <c r="AL4" s="21" t="str">
         <f aca="false">IF(AND(AC4="Sold",AD4&lt;&gt;"",Z4&lt;&gt;""),AD4-Z4,"")</f>
@@ -2086,7 +2098,7 @@
       </c>
       <c r="AM4" s="20" t="n">
         <f aca="false">IF(AND(AC4="Sold",N(AA4)&gt;0,AE4&lt;&gt;""),1-AE4/AA4,"")</f>
-        <v>0.329411764705882</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="AN4" s="21" t="str">
         <f aca="true">IF(AND(AC4&lt;&gt;"Sold",AC4&lt;&gt;"",Z4&lt;&gt;""),TODAY()-Z4,"")</f>
@@ -2136,7 +2148,7 @@
         <v>46215</v>
       </c>
       <c r="P5" s="16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q5" s="4" t="s">
         <v>77</v>
@@ -2146,10 +2158,10 @@
       </c>
       <c r="S5" s="18" t="n">
         <f aca="false">IF(OR(P5="",R5=""),"",P5*R5)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U5" s="14" t="n">
         <v>0</v>
@@ -2162,14 +2174,14 @@
       </c>
       <c r="X5" s="18" t="n">
         <f aca="false">IF(S5="","",S5+N(T5)+N(U5)+N(V5)+N(W5))</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>78</v>
       </c>
       <c r="Z5" s="15"/>
       <c r="AA5" s="14" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB5" s="19"/>
       <c r="AC5" s="4" t="s">
@@ -2177,10 +2189,10 @@
       </c>
       <c r="AD5" s="15"/>
       <c r="AE5" s="14" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="AF5" s="14" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="AG5" s="14"/>
       <c r="AH5" s="18" t="n">
@@ -2189,15 +2201,15 @@
       </c>
       <c r="AI5" s="18" t="n">
         <f aca="false">IF(AND(AC5="Sold",AF5&lt;&gt;"",X5&lt;&gt;""),AF5-N(AG5)-X5,"")</f>
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AJ5" s="20" t="n">
         <f aca="false">IF(AND(AI5&lt;&gt;"",N(AE5)&gt;0),AI5/AE5,"")</f>
-        <v>0.896739130434783</v>
+        <v>0.890625</v>
       </c>
       <c r="AK5" s="20" t="n">
         <f aca="false">IF(AND(AI5&lt;&gt;"",N(X5)&gt;0),AI5/X5,"")</f>
-        <v>8.68421052631579</v>
+        <v>8.14285714285714</v>
       </c>
       <c r="AL5" s="21" t="str">
         <f aca="false">IF(AND(AC5="Sold",AD5&lt;&gt;"",Z5&lt;&gt;""),AD5-Z5,"")</f>
@@ -2255,7 +2267,7 @@
         <v>46215</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q6" s="4" t="s">
         <v>77</v>
@@ -2265,10 +2277,10 @@
       </c>
       <c r="S6" s="18" t="n">
         <f aca="false">IF(OR(P6="",R6=""),"",P6*R6)</f>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T6" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="U6" s="14" t="n">
         <v>0</v>
@@ -2281,14 +2293,14 @@
       </c>
       <c r="X6" s="18" t="n">
         <f aca="false">IF(S6="","",S6+N(T6)+N(U6)+N(V6)+N(W6))</f>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>78</v>
       </c>
       <c r="Z6" s="15"/>
       <c r="AA6" s="14" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="AB6" s="19"/>
       <c r="AC6" s="4" t="s">
@@ -2296,10 +2308,10 @@
       </c>
       <c r="AD6" s="15"/>
       <c r="AE6" s="14" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="AF6" s="14" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="AG6" s="14"/>
       <c r="AH6" s="18" t="n">
@@ -2308,15 +2320,15 @@
       </c>
       <c r="AI6" s="18" t="n">
         <f aca="false">IF(AND(AC6="Sold",AF6&lt;&gt;"",X6&lt;&gt;""),AF6-N(AG6)-X6,"")</f>
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="AJ6" s="20" t="n">
         <f aca="false">IF(AND(AI6&lt;&gt;"",N(AE6)&gt;0),AI6/AE6,"")</f>
-        <v>0.675925925925926</v>
+        <v>0.672131147540984</v>
       </c>
       <c r="AK6" s="20" t="n">
         <f aca="false">IF(AND(AI6&lt;&gt;"",N(X6)&gt;0),AI6/X6,"")</f>
-        <v>2.08571428571429</v>
+        <v>2.05</v>
       </c>
       <c r="AL6" s="21" t="str">
         <f aca="false">IF(AND(AC6="Sold",AD6&lt;&gt;"",Z6&lt;&gt;""),AD6-Z6,"")</f>
@@ -2324,7 +2336,7 @@
       </c>
       <c r="AM6" s="20" t="n">
         <f aca="false">IF(AND(AC6="Sold",N(AA6)&gt;0,AE6&lt;&gt;""),1-AE6/AA6,"")</f>
-        <v>0.372093023255814</v>
+        <v>0.374358974358974</v>
       </c>
       <c r="AN6" s="21" t="str">
         <f aca="true">IF(AND(AC6&lt;&gt;"Sold",AC6&lt;&gt;"",Z6&lt;&gt;""),TODAY()-Z6,"")</f>
@@ -2372,7 +2384,7 @@
         <v>46204</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q7" s="4" t="s">
         <v>77</v>
@@ -2382,7 +2394,7 @@
       </c>
       <c r="S7" s="18" t="n">
         <f aca="false">IF(OR(P7="",R7=""),"",P7*R7)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T7" s="14" t="n">
         <v>10</v>
@@ -2398,14 +2410,14 @@
       </c>
       <c r="X7" s="18" t="n">
         <f aca="false">IF(S7="","",S7+N(T7)+N(U7)+N(V7)+N(W7))</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>101</v>
       </c>
       <c r="Z7" s="15"/>
       <c r="AA7" s="14" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AB7" s="19"/>
       <c r="AC7" s="4" t="s">
@@ -2413,10 +2425,10 @@
       </c>
       <c r="AD7" s="15"/>
       <c r="AE7" s="14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AF7" s="14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AG7" s="14"/>
       <c r="AH7" s="18" t="n">
@@ -2425,15 +2437,15 @@
       </c>
       <c r="AI7" s="18" t="n">
         <f aca="false">IF(AND(AC7="Sold",AF7&lt;&gt;"",X7&lt;&gt;""),AF7-N(AG7)-X7,"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ7" s="20" t="n">
         <f aca="false">IF(AND(AI7&lt;&gt;"",N(AE7)&gt;0),AI7/AE7,"")</f>
-        <v>0.126984126984127</v>
+        <v>0.138461538461538</v>
       </c>
       <c r="AK7" s="20" t="n">
         <f aca="false">IF(AND(AI7&lt;&gt;"",N(X7)&gt;0),AI7/X7,"")</f>
-        <v>0.173913043478261</v>
+        <v>0.191489361702128</v>
       </c>
       <c r="AL7" s="21" t="str">
         <f aca="false">IF(AND(AC7="Sold",AD7&lt;&gt;"",Z7&lt;&gt;""),AD7-Z7,"")</f>
@@ -2441,7 +2453,7 @@
       </c>
       <c r="AM7" s="20" t="n">
         <f aca="false">IF(AND(AC7="Sold",N(AA7)&gt;0,AE7&lt;&gt;""),1-AE7/AA7,"")</f>
-        <v>0.3</v>
+        <v>0.301075268817204</v>
       </c>
       <c r="AN7" s="21" t="str">
         <f aca="true">IF(AND(AC7&lt;&gt;"Sold",AC7&lt;&gt;"",Z7&lt;&gt;""),TODAY()-Z7,"")</f>
@@ -2502,7 +2514,7 @@
         <v>10</v>
       </c>
       <c r="T8" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U8" s="14" t="n">
         <v>0</v>
@@ -2515,14 +2527,14 @@
       </c>
       <c r="X8" s="18" t="n">
         <f aca="false">IF(S8="","",S8+N(T8)+N(U8)+N(V8)+N(W8))</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>104</v>
       </c>
       <c r="Z8" s="15"/>
       <c r="AA8" s="14" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AB8" s="19"/>
       <c r="AC8" s="4" t="s">
@@ -2530,10 +2542,10 @@
       </c>
       <c r="AD8" s="15"/>
       <c r="AE8" s="14" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="AF8" s="14" t="n">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="AG8" s="14"/>
       <c r="AH8" s="18" t="n">
@@ -2542,15 +2554,15 @@
       </c>
       <c r="AI8" s="18" t="n">
         <f aca="false">IF(AND(AC8="Sold",AF8&lt;&gt;"",X8&lt;&gt;""),AF8-N(AG8)-X8,"")</f>
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="AJ8" s="20" t="n">
         <f aca="false">IF(AND(AI8&lt;&gt;"",N(AE8)&gt;0),AI8/AE8,"")</f>
-        <v>0.860927152317881</v>
+        <v>0.86013986013986</v>
       </c>
       <c r="AK8" s="20" t="n">
         <f aca="false">IF(AND(AI8&lt;&gt;"",N(X8)&gt;0),AI8/X8,"")</f>
-        <v>6.19047619047619</v>
+        <v>6.15</v>
       </c>
       <c r="AL8" s="21" t="str">
         <f aca="false">IF(AND(AC8="Sold",AD8&lt;&gt;"",Z8&lt;&gt;""),AD8-Z8,"")</f>
@@ -2558,7 +2570,7 @@
       </c>
       <c r="AM8" s="20" t="n">
         <f aca="false">IF(AND(AC8="Sold",N(AA8)&gt;0,AE8&lt;&gt;""),1-AE8/AA8,"")</f>
-        <v>-0.495049504950495</v>
+        <v>-0.505263157894737</v>
       </c>
       <c r="AN8" s="21" t="str">
         <f aca="true">IF(AND(AC8&lt;&gt;"Sold",AC8&lt;&gt;"",Z8&lt;&gt;""),TODAY()-Z8,"")</f>
@@ -2639,7 +2651,7 @@
       </c>
       <c r="Z9" s="15"/>
       <c r="AA9" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB9" s="19"/>
       <c r="AC9" s="4" t="s">
@@ -2647,10 +2659,10 @@
       </c>
       <c r="AD9" s="15"/>
       <c r="AE9" s="14" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AF9" s="14" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG9" s="14"/>
       <c r="AH9" s="18" t="n">
@@ -2659,15 +2671,15 @@
       </c>
       <c r="AI9" s="18" t="n">
         <f aca="false">IF(AND(AC9="Sold",AF9&lt;&gt;"",X9&lt;&gt;""),AF9-N(AG9)-X9,"")</f>
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AJ9" s="20" t="n">
         <f aca="false">IF(AND(AI9&lt;&gt;"",N(AE9)&gt;0),AI9/AE9,"")</f>
-        <v>0.795348837209302</v>
+        <v>0.793427230046948</v>
       </c>
       <c r="AK9" s="20" t="n">
         <f aca="false">IF(AND(AI9&lt;&gt;"",N(X9)&gt;0),AI9/X9,"")</f>
-        <v>3.88636363636364</v>
+        <v>3.84090909090909</v>
       </c>
       <c r="AL9" s="21" t="str">
         <f aca="false">IF(AND(AC9="Sold",AD9&lt;&gt;"",Z9&lt;&gt;""),AD9-Z9,"")</f>
@@ -2675,7 +2687,7 @@
       </c>
       <c r="AM9" s="20" t="n">
         <f aca="false">IF(AND(AC9="Sold",N(AA9)&gt;0,AE9&lt;&gt;""),1-AE9/AA9,"")</f>
-        <v>-1.00934579439252</v>
+        <v>-1.00943396226415</v>
       </c>
       <c r="AN9" s="21" t="str">
         <f aca="true">IF(AND(AC9&lt;&gt;"Sold",AC9&lt;&gt;"",Z9&lt;&gt;""),TODAY()-Z9,"")</f>
@@ -2723,7 +2735,7 @@
         <v>46215</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="Q10" s="4" t="s">
         <v>77</v>
@@ -2733,10 +2745,10 @@
       </c>
       <c r="S10" s="18" t="n">
         <f aca="false">IF(OR(P10="",R10=""),"",P10*R10)</f>
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="T10" s="14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U10" s="14" t="n">
         <v>0</v>
@@ -2749,14 +2761,14 @@
       </c>
       <c r="X10" s="18" t="n">
         <f aca="false">IF(S10="","",S10+N(T10)+N(U10)+N(V10)+N(W10))</f>
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>104</v>
       </c>
       <c r="Z10" s="15"/>
       <c r="AA10" s="14" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="AB10" s="19"/>
       <c r="AC10" s="4" t="s">
@@ -2764,10 +2776,10 @@
       </c>
       <c r="AD10" s="15"/>
       <c r="AE10" s="14" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="AF10" s="14" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="AG10" s="14"/>
       <c r="AH10" s="18" t="n">
@@ -2776,15 +2788,15 @@
       </c>
       <c r="AI10" s="18" t="n">
         <f aca="false">IF(AND(AC10="Sold",AF10&lt;&gt;"",X10&lt;&gt;""),AF10-N(AG10)-X10,"")</f>
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="AJ10" s="20" t="n">
         <f aca="false">IF(AND(AI10&lt;&gt;"",N(AE10)&gt;0),AI10/AE10,"")</f>
-        <v>0.72463768115942</v>
+        <v>0.730538922155689</v>
       </c>
       <c r="AK10" s="20" t="n">
         <f aca="false">IF(AND(AI10&lt;&gt;"",N(X10)&gt;0),AI10/X10,"")</f>
-        <v>2.63157894736842</v>
+        <v>2.71111111111111</v>
       </c>
       <c r="AL10" s="21" t="str">
         <f aca="false">IF(AND(AC10="Sold",AD10&lt;&gt;"",Z10&lt;&gt;""),AD10-Z10,"")</f>
@@ -2792,7 +2804,7 @@
       </c>
       <c r="AM10" s="20" t="n">
         <f aca="false">IF(AND(AC10="Sold",N(AA10)&gt;0,AE10&lt;&gt;""),1-AE10/AA10,"")</f>
-        <v>-0.5</v>
+        <v>-0.491071428571429</v>
       </c>
       <c r="AN10" s="21" t="str">
         <f aca="true">IF(AND(AC10&lt;&gt;"Sold",AC10&lt;&gt;"",Z10&lt;&gt;""),TODAY()-Z10,"")</f>
@@ -2840,7 +2852,7 @@
         <v>46215</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>77</v>
@@ -2850,10 +2862,10 @@
       </c>
       <c r="S11" s="18" t="n">
         <f aca="false">IF(OR(P11="",R11=""),"",P11*R11)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" s="14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U11" s="14" t="n">
         <v>0</v>
@@ -2866,46 +2878,50 @@
       </c>
       <c r="X11" s="18" t="n">
         <f aca="false">IF(S11="","",S11+N(T11)+N(U11)+N(V11)+N(W11))</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y11" s="4" t="s">
         <v>104</v>
       </c>
       <c r="Z11" s="15"/>
       <c r="AA11" s="14" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="AB11" s="19"/>
       <c r="AC11" s="4" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD11" s="15"/>
-      <c r="AE11" s="14"/>
-      <c r="AF11" s="14"/>
+      <c r="AE11" s="14" t="n">
+        <v>164</v>
+      </c>
+      <c r="AF11" s="14" t="n">
+        <v>164</v>
+      </c>
       <c r="AG11" s="14"/>
-      <c r="AH11" s="18" t="str">
+      <c r="AH11" s="18" t="n">
         <f aca="false">IF(AND(AC11="Sold",AE11&lt;&gt;"",AF11&lt;&gt;""),AE11-AF11,"")</f>
-        <v/>
-      </c>
-      <c r="AI11" s="18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="18" t="n">
         <f aca="false">IF(AND(AC11="Sold",AF11&lt;&gt;"",X11&lt;&gt;""),AF11-N(AG11)-X11,"")</f>
-        <v/>
-      </c>
-      <c r="AJ11" s="20" t="str">
+        <v>141</v>
+      </c>
+      <c r="AJ11" s="20" t="n">
         <f aca="false">IF(AND(AI11&lt;&gt;"",N(AE11)&gt;0),AI11/AE11,"")</f>
-        <v/>
-      </c>
-      <c r="AK11" s="20" t="str">
+        <v>0.859756097560976</v>
+      </c>
+      <c r="AK11" s="20" t="n">
         <f aca="false">IF(AND(AI11&lt;&gt;"",N(X11)&gt;0),AI11/X11,"")</f>
-        <v/>
+        <v>6.1304347826087</v>
       </c>
       <c r="AL11" s="21" t="str">
         <f aca="false">IF(AND(AC11="Sold",AD11&lt;&gt;"",Z11&lt;&gt;""),AD11-Z11,"")</f>
         <v/>
       </c>
-      <c r="AM11" s="20" t="str">
+      <c r="AM11" s="20" t="n">
         <f aca="false">IF(AND(AC11="Sold",N(AA11)&gt;0,AE11&lt;&gt;""),1-AE11/AA11,"")</f>
-        <v/>
+        <v>-0.504587155963303</v>
       </c>
       <c r="AN11" s="21" t="str">
         <f aca="true">IF(AND(AC11&lt;&gt;"Sold",AC11&lt;&gt;"",Z11&lt;&gt;""),TODAY()-Z11,"")</f>
@@ -2915,18 +2931,18 @@
         <v>86</v>
       </c>
       <c r="AP11" s="4" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -2986,7 +3002,7 @@
       </c>
       <c r="Z12" s="15"/>
       <c r="AA12" s="14" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="AB12" s="19"/>
       <c r="AC12" s="4" t="s">
@@ -2994,10 +3010,10 @@
       </c>
       <c r="AD12" s="15"/>
       <c r="AE12" s="14" t="n">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="AF12" s="14" t="n">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="AG12" s="14"/>
       <c r="AH12" s="18" t="n">
@@ -3006,15 +3022,15 @@
       </c>
       <c r="AI12" s="18" t="n">
         <f aca="false">IF(AND(AC12="Sold",AF12&lt;&gt;"",X12&lt;&gt;""),AF12-N(AG12)-X12,"")</f>
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="AJ12" s="20" t="n">
         <f aca="false">IF(AND(AI12&lt;&gt;"",N(AE12)&gt;0),AI12/AE12,"")</f>
-        <v>0.886904761904762</v>
+        <v>0.880503144654088</v>
       </c>
       <c r="AK12" s="20" t="n">
         <f aca="false">IF(AND(AI12&lt;&gt;"",N(X12)&gt;0),AI12/X12,"")</f>
-        <v>7.8421052631579</v>
+        <v>7.36842105263158</v>
       </c>
       <c r="AL12" s="21" t="str">
         <f aca="false">IF(AND(AC12="Sold",AD12&lt;&gt;"",Z12&lt;&gt;""),AD12-Z12,"")</f>
@@ -3022,7 +3038,7 @@
       </c>
       <c r="AM12" s="20" t="n">
         <f aca="false">IF(AND(AC12="Sold",N(AA12)&gt;0,AE12&lt;&gt;""),1-AE12/AA12,"")</f>
-        <v>-0.806451612903226</v>
+        <v>-0.806818181818182</v>
       </c>
       <c r="AN12" s="21" t="str">
         <f aca="true">IF(AND(AC12&lt;&gt;"Sold",AC12&lt;&gt;"",Z12&lt;&gt;""),TODAY()-Z12,"")</f>
@@ -3037,7 +3053,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>83</v>
@@ -3045,10 +3061,10 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
@@ -3103,7 +3119,7 @@
       </c>
       <c r="Z13" s="15"/>
       <c r="AA13" s="14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AB13" s="19"/>
       <c r="AC13" s="4" t="s">
@@ -3111,10 +3127,10 @@
       </c>
       <c r="AD13" s="15"/>
       <c r="AE13" s="14" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AF13" s="14" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AG13" s="14"/>
       <c r="AH13" s="18" t="n">
@@ -3123,15 +3139,15 @@
       </c>
       <c r="AI13" s="18" t="n">
         <f aca="false">IF(AND(AC13="Sold",AF13&lt;&gt;"",X13&lt;&gt;""),AF13-N(AG13)-X13,"")</f>
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="AJ13" s="20" t="n">
         <f aca="false">IF(AND(AI13&lt;&gt;"",N(AE13)&gt;0),AI13/AE13,"")</f>
-        <v>0.895</v>
+        <v>0.891752577319588</v>
       </c>
       <c r="AK13" s="20" t="n">
         <f aca="false">IF(AND(AI13&lt;&gt;"",N(X13)&gt;0),AI13/X13,"")</f>
-        <v>8.52380952380952</v>
+        <v>8.23809523809524</v>
       </c>
       <c r="AL13" s="21" t="str">
         <f aca="false">IF(AND(AC13="Sold",AD13&lt;&gt;"",Z13&lt;&gt;""),AD13-Z13,"")</f>
@@ -3154,17 +3170,17 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>92</v>
@@ -3174,22 +3190,24 @@
         <v>96</v>
       </c>
       <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="K14" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="L14" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="M14" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="N14" s="14"/>
       <c r="O14" s="15" t="n">
         <v>46223</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="Q14" s="4" t="s">
         <v>77</v>
@@ -3199,10 +3217,10 @@
       </c>
       <c r="S14" s="18" t="n">
         <f aca="false">IF(OR(P14="",R14=""),"",P14*R14)</f>
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="T14" s="14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U14" s="14" t="n">
         <v>0</v>
@@ -3215,14 +3233,14 @@
       </c>
       <c r="X14" s="18" t="n">
         <f aca="false">IF(S14="","",S14+N(T14)+N(U14)+N(V14)+N(W14))</f>
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Z14" s="15"/>
       <c r="AA14" s="14" t="n">
-        <v>1206</v>
+        <v>1252</v>
       </c>
       <c r="AB14" s="19"/>
       <c r="AC14" s="4" t="s">
@@ -3230,27 +3248,27 @@
       </c>
       <c r="AD14" s="15"/>
       <c r="AE14" s="14" t="n">
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="AF14" s="14" t="n">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="AG14" s="14"/>
       <c r="AH14" s="18" t="n">
         <f aca="false">IF(AND(AC14="Sold",AE14&lt;&gt;"",AF14&lt;&gt;""),AE14-AF14,"")</f>
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AI14" s="18" t="n">
         <f aca="false">IF(AND(AC14="Sold",AF14&lt;&gt;"",X14&lt;&gt;""),AF14-N(AG14)-X14,"")</f>
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AJ14" s="20" t="n">
         <f aca="false">IF(AND(AI14&lt;&gt;"",N(AE14)&gt;0),AI14/AE14,"")</f>
-        <v>0.333333333333333</v>
+        <v>0.333865814696486</v>
       </c>
       <c r="AK14" s="20" t="n">
         <f aca="false">IF(AND(AI14&lt;&gt;"",N(X14)&gt;0),AI14/X14,"")</f>
-        <v>0.700348432055749</v>
+        <v>0.701342281879195</v>
       </c>
       <c r="AL14" s="21" t="str">
         <f aca="false">IF(AND(AC14="Sold",AD14&lt;&gt;"",Z14&lt;&gt;""),AD14-Z14,"")</f>
@@ -3268,25 +3286,25 @@
         <v>80</v>
       </c>
       <c r="AP14" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>99</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
         <v>84</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
@@ -3308,7 +3326,7 @@
         <v>46215</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q15" s="4" t="s">
         <v>77</v>
@@ -3318,10 +3336,10 @@
       </c>
       <c r="S15" s="18" t="n">
         <f aca="false">IF(OR(P15="",R15=""),"",P15*R15)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T15" s="14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U15" s="14" t="n">
         <v>0</v>
@@ -3334,18 +3352,18 @@
       </c>
       <c r="X15" s="18" t="n">
         <f aca="false">IF(S15="","",S15+N(T15)+N(U15)+N(V15)+N(W15))</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Y15" s="4" t="s">
         <v>104</v>
       </c>
       <c r="Z15" s="15"/>
       <c r="AA15" s="14" t="n">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="AB15" s="19"/>
       <c r="AC15" s="4" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="AD15" s="15"/>
       <c r="AE15" s="14"/>
@@ -3383,7 +3401,7 @@
         <v>86</v>
       </c>
       <c r="AP15" s="4" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3421,7 +3439,7 @@
         <v>46215</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q16" s="4" t="s">
         <v>77</v>
@@ -3431,10 +3449,10 @@
       </c>
       <c r="S16" s="18" t="n">
         <f aca="false">IF(OR(P16="",R16=""),"",P16*R16)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T16" s="14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="U16" s="14" t="n">
         <v>0</v>
@@ -3447,46 +3465,50 @@
       </c>
       <c r="X16" s="18" t="n">
         <f aca="false">IF(S16="","",S16+N(T16)+N(U16)+N(V16)+N(W16))</f>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="Z16" s="15"/>
       <c r="AA16" s="14" t="n">
-        <v>1103</v>
+        <v>858</v>
       </c>
       <c r="AB16" s="19"/>
       <c r="AC16" s="4" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD16" s="15"/>
-      <c r="AE16" s="14"/>
-      <c r="AF16" s="14"/>
+      <c r="AE16" s="14" t="n">
+        <v>317</v>
+      </c>
+      <c r="AF16" s="14" t="n">
+        <v>317</v>
+      </c>
       <c r="AG16" s="14"/>
-      <c r="AH16" s="18" t="str">
+      <c r="AH16" s="18" t="n">
         <f aca="false">IF(AND(AC16="Sold",AE16&lt;&gt;"",AF16&lt;&gt;""),AE16-AF16,"")</f>
-        <v/>
-      </c>
-      <c r="AI16" s="18" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="18" t="n">
         <f aca="false">IF(AND(AC16="Sold",AF16&lt;&gt;"",X16&lt;&gt;""),AF16-N(AG16)-X16,"")</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="20" t="str">
+        <v>299</v>
+      </c>
+      <c r="AJ16" s="20" t="n">
         <f aca="false">IF(AND(AI16&lt;&gt;"",N(AE16)&gt;0),AI16/AE16,"")</f>
-        <v/>
-      </c>
-      <c r="AK16" s="20" t="str">
+        <v>0.943217665615142</v>
+      </c>
+      <c r="AK16" s="20" t="n">
         <f aca="false">IF(AND(AI16&lt;&gt;"",N(X16)&gt;0),AI16/X16,"")</f>
-        <v/>
+        <v>16.6111111111111</v>
       </c>
       <c r="AL16" s="21" t="str">
         <f aca="false">IF(AND(AC16="Sold",AD16&lt;&gt;"",Z16&lt;&gt;""),AD16-Z16,"")</f>
         <v/>
       </c>
-      <c r="AM16" s="20" t="str">
+      <c r="AM16" s="20" t="n">
         <f aca="false">IF(AND(AC16="Sold",N(AA16)&gt;0,AE16&lt;&gt;""),1-AE16/AA16,"")</f>
-        <v/>
+        <v>0.630536130536131</v>
       </c>
       <c r="AN16" s="21" t="str">
         <f aca="true">IF(AND(AC16&lt;&gt;"Sold",AC16&lt;&gt;"",Z16&lt;&gt;""),TODAY()-Z16,"")</f>
@@ -3496,79 +3518,129 @@
         <v>86</v>
       </c>
       <c r="AP16" s="4" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="H17" s="4" t="s">
+        <v>73</v>
+      </c>
       <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
+      <c r="J17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>76</v>
+      </c>
       <c r="N17" s="14"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="18" t="str">
+      <c r="O17" s="15" t="n">
+        <v>46235</v>
+      </c>
+      <c r="P17" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="18" t="n">
         <f aca="false">IF(OR(P17="",R17=""),"",P17*R17)</f>
-        <v/>
-      </c>
-      <c r="T17" s="14"/>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="18" t="str">
+        <v>37</v>
+      </c>
+      <c r="T17" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="U17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="18" t="n">
         <f aca="false">IF(S17="","",S17+N(T17)+N(U17)+N(V17)+N(W17))</f>
-        <v/>
-      </c>
-      <c r="Y17" s="4"/>
+        <v>47</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="Z17" s="15"/>
-      <c r="AA17" s="14"/>
+      <c r="AA17" s="14" t="n">
+        <v>550</v>
+      </c>
       <c r="AB17" s="19"/>
-      <c r="AC17" s="4"/>
+      <c r="AC17" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="AD17" s="15"/>
-      <c r="AE17" s="14"/>
-      <c r="AF17" s="14"/>
-      <c r="AG17" s="14"/>
-      <c r="AH17" s="18" t="str">
+      <c r="AE17" s="14" t="n">
+        <v>338</v>
+      </c>
+      <c r="AF17" s="14" t="n">
+        <v>272</v>
+      </c>
+      <c r="AG17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="18" t="n">
         <f aca="false">IF(AND(AC17="Sold",AE17&lt;&gt;"",AF17&lt;&gt;""),AE17-AF17,"")</f>
-        <v/>
-      </c>
-      <c r="AI17" s="18" t="str">
+        <v>66</v>
+      </c>
+      <c r="AI17" s="18" t="n">
         <f aca="false">IF(AND(AC17="Sold",AF17&lt;&gt;"",X17&lt;&gt;""),AF17-N(AG17)-X17,"")</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="20" t="str">
+        <v>225</v>
+      </c>
+      <c r="AJ17" s="20" t="n">
         <f aca="false">IF(AND(AI17&lt;&gt;"",N(AE17)&gt;0),AI17/AE17,"")</f>
-        <v/>
-      </c>
-      <c r="AK17" s="20" t="str">
+        <v>0.665680473372781</v>
+      </c>
+      <c r="AK17" s="20" t="n">
         <f aca="false">IF(AND(AI17&lt;&gt;"",N(X17)&gt;0),AI17/X17,"")</f>
-        <v/>
+        <v>4.78723404255319</v>
       </c>
       <c r="AL17" s="21" t="str">
         <f aca="false">IF(AND(AC17="Sold",AD17&lt;&gt;"",Z17&lt;&gt;""),AD17-Z17,"")</f>
         <v/>
       </c>
-      <c r="AM17" s="20" t="str">
+      <c r="AM17" s="20" t="n">
         <f aca="false">IF(AND(AC17="Sold",N(AA17)&gt;0,AE17&lt;&gt;""),1-AE17/AA17,"")</f>
-        <v/>
+        <v>0.385454545454546</v>
       </c>
       <c r="AN17" s="21" t="str">
         <f aca="true">IF(AND(AC17&lt;&gt;"Sold",AC17&lt;&gt;"",Z17&lt;&gt;""),TODAY()-Z17,"")</f>
         <v/>
       </c>
-      <c r="AO17" s="4"/>
-      <c r="AP17" s="4"/>
+      <c r="AO17" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP17" s="4" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
@@ -38158,71 +38230,71 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B4" s="23" t="n">
         <f aca="false">COUNTA(Bags!$B$3:$B$503)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">COUNTIF(Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">IFERROR(B5/B4,0)</f>
-        <v>0.785714285714286</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B7" s="25" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>2219</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B8" s="26" t="n">
         <f aca="false">SUM(Bags!$AI$3:$AI$503)</f>
-        <v>1498</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B9" s="24" t="n">
         <f aca="false">IFERROR(B8/B7,0)</f>
-        <v>0.675078864353312</v>
+        <v>0.710070558050032</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B10" s="23" t="n">
         <f aca="false">IFERROR(AVERAGE(Bags!$AL$3:$AL$503),0)</f>
@@ -38231,25 +38303,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B11" s="25" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
-        <v>85</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B12" s="23" t="n">
         <f aca="false">COUNTIF(Bags!$AO$3:$AO$503,"Estimated")+COUNTIF(Bags!$AO$3:$AO$503,"Unknown")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38257,16 +38329,16 @@
         <v>37</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>79</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F16" s="29" t="s">
         <v>60</v>
@@ -38275,13 +38347,13 @@
         <v>61</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38290,27 +38362,27 @@
       </c>
       <c r="B17" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$L$3:$L$503,$A17)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">COUNTIFS(Bags!$L$3:$L$503,$A17,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17" s="30" t="n">
         <f aca="false">IFERROR(C17/B17,0)</f>
-        <v>0.769230769230769</v>
+        <v>0.928571428571429</v>
       </c>
       <c r="E17" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$L$3:$L$503,$A17,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>1616</v>
+        <v>2492</v>
       </c>
       <c r="F17" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$L$3:$L$503,$A17)</f>
-        <v>1297</v>
+        <v>2005</v>
       </c>
       <c r="G17" s="30" t="n">
         <f aca="false">IFERROR(F17/E17,0)</f>
-        <v>0.80259900990099</v>
+        <v>0.804574638844302</v>
       </c>
       <c r="H17" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$L$3:$L$503,$A17,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -38318,16 +38390,16 @@
       </c>
       <c r="I17" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$L$3:$L$503,$A17,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>-0.240876072893571</v>
+        <v>-0.145570433385509</v>
       </c>
       <c r="J17" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$L$3:$L$503,$A17,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
-        <v>85</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B18" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$L$3:$L$503,$A18)</f>
@@ -38343,15 +38415,15 @@
       </c>
       <c r="E18" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$L$3:$L$503,$A18,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="F18" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$L$3:$L$503,$A18)</f>
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G18" s="30" t="n">
         <f aca="false">IFERROR(F18/E18,0)</f>
-        <v>0.333333333333333</v>
+        <v>0.333865814696486</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$L$3:$L$503,$A18,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -38368,7 +38440,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38376,16 +38448,16 @@
         <v>27</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C22" s="29" t="s">
         <v>79</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F22" s="29" t="s">
         <v>60</v>
@@ -38394,13 +38466,13 @@
         <v>61</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I22" s="29" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J22" s="29" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38413,23 +38485,23 @@
       </c>
       <c r="C23" s="19" t="n">
         <f aca="false">COUNTIFS(Bags!$B$3:$B$503,$A23,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="30" t="n">
         <f aca="false">IFERROR(C23/B23,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$B$3:$B$503,$A23,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="F23" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$B$3:$B$503,$A23)</f>
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="G23" s="30" t="n">
         <f aca="false">IFERROR(F23/E23,0)</f>
-        <v>0</v>
+        <v>0.943217665615142</v>
       </c>
       <c r="H23" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$B$3:$B$503,$A23,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -38437,11 +38509,11 @@
       </c>
       <c r="I23" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$B$3:$B$503,$A23,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>0</v>
+        <v>0.630536130536131</v>
       </c>
       <c r="J23" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$B$3:$B$503,$A23,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38454,23 +38526,23 @@
       </c>
       <c r="C24" s="19" t="n">
         <f aca="false">COUNTIFS(Bags!$B$3:$B$503,$A24,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="30" t="n">
         <f aca="false">IFERROR(C24/B24,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
       <c r="E24" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$B$3:$B$503,$A24,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>314</v>
+        <v>464</v>
       </c>
       <c r="F24" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$B$3:$B$503,$A24)</f>
-        <v>247</v>
+        <v>376</v>
       </c>
       <c r="G24" s="30" t="n">
         <f aca="false">IFERROR(F24/E24,0)</f>
-        <v>0.786624203821656</v>
+        <v>0.810344827586207</v>
       </c>
       <c r="H24" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$B$3:$B$503,$A24,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -38478,16 +38550,16 @@
       </c>
       <c r="I24" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$B$3:$B$503,$A24,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>-0.335294117647059</v>
+        <v>-0.390417940876657</v>
       </c>
       <c r="J24" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$B$3:$B$503,$A24,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B25" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A25)</f>
@@ -38544,15 +38616,15 @@
       </c>
       <c r="E26" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$B$3:$B$503,$A26,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>787</v>
+        <v>818</v>
       </c>
       <c r="F26" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$B$3:$B$503,$A26)</f>
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="G26" s="30" t="n">
         <f aca="false">IFERROR(F26/E26,0)</f>
-        <v>0.465057179161372</v>
+        <v>0.464547677261614</v>
       </c>
       <c r="H26" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$B$3:$B$503,$A26,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -38573,11 +38645,11 @@
       </c>
       <c r="B27" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A27)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="19" t="n">
         <f aca="false">COUNTIFS(Bags!$B$3:$B$503,$A27,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="30" t="n">
         <f aca="false">IFERROR(C27/B27,0)</f>
@@ -38585,15 +38657,15 @@
       </c>
       <c r="E27" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$B$3:$B$503,$A27,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>276</v>
+        <v>619</v>
       </c>
       <c r="F27" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$B$3:$B$503,$A27)</f>
-        <v>222</v>
+        <v>447</v>
       </c>
       <c r="G27" s="30" t="n">
         <f aca="false">IFERROR(F27/E27,0)</f>
-        <v>0.804347826086957</v>
+        <v>0.722132471728595</v>
       </c>
       <c r="H27" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$B$3:$B$503,$A27,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -38601,7 +38673,7 @@
       </c>
       <c r="I27" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$B$3:$B$503,$A27,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>-0.217179294823706</v>
+        <v>-0.0156682206682207</v>
       </c>
       <c r="J27" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$B$3:$B$503,$A27,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
@@ -38610,7 +38682,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B28" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A28)</f>
@@ -38651,7 +38723,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B29" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A29)</f>
@@ -38708,15 +38780,15 @@
       </c>
       <c r="E30" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$B$3:$B$503,$A30,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="F30" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$B$3:$B$503,$A30)</f>
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="G30" s="30" t="n">
         <f aca="false">IFERROR(F30/E30,0)</f>
-        <v>0.901408450704225</v>
+        <v>0.905494505494506</v>
       </c>
       <c r="H30" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$B$3:$B$503,$A30,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -38724,7 +38796,7 @@
       </c>
       <c r="I30" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$B$3:$B$503,$A30,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>-0.147234054800829</v>
+        <v>-0.152631578947368</v>
       </c>
       <c r="J30" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$B$3:$B$503,$A30,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
@@ -38749,15 +38821,15 @@
       </c>
       <c r="E31" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$B$3:$B$503,$A31,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="F31" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$B$3:$B$503,$A31)</f>
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="G31" s="30" t="n">
         <f aca="false">IFERROR(F31/E31,0)</f>
-        <v>0.670673076923077</v>
+        <v>0.674157303370787</v>
       </c>
       <c r="H31" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$B$3:$B$503,$A31,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -38765,16 +38837,16 @@
       </c>
       <c r="I31" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$B$3:$B$503,$A31,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>-0.403115264797508</v>
+        <v>-0.399810040672792</v>
       </c>
       <c r="J31" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$B$3:$B$503,$A31,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B32" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A32)</f>
@@ -38815,7 +38887,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B33" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A33)</f>
@@ -38856,7 +38928,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B34" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A34)</f>
@@ -38897,7 +38969,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B35" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A35)</f>
@@ -38938,7 +39010,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B36" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A36)</f>
@@ -38979,7 +39051,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B37" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A37)</f>
@@ -39020,7 +39092,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="B38" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$B$3:$B$503,$A38)</f>
@@ -39061,7 +39133,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39069,16 +39141,16 @@
         <v>50</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C42" s="29" t="s">
         <v>79</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F42" s="29" t="s">
         <v>60</v>
@@ -39087,13 +39159,13 @@
         <v>61</v>
       </c>
       <c r="H42" s="29" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I42" s="29" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J42" s="29" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39114,15 +39186,15 @@
       </c>
       <c r="E43" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$Y$3:$Y$503,$A43,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>681</v>
+        <v>732</v>
       </c>
       <c r="F43" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$Y$3:$Y$503,$A43)</f>
-        <v>560</v>
+        <v>604</v>
       </c>
       <c r="G43" s="30" t="n">
         <f aca="false">IFERROR(F43/E43,0)</f>
-        <v>0.822320117474302</v>
+        <v>0.825136612021858</v>
       </c>
       <c r="H43" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$Y$3:$Y$503,$A43,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -39130,7 +39202,7 @@
       </c>
       <c r="I43" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$Y$3:$Y$503,$A43,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>0.275521545827633</v>
+        <v>0.276923076923077</v>
       </c>
       <c r="J43" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$Y$3:$Y$503,$A43,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
@@ -39139,15 +39211,15 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B44" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$Y$3:$Y$503,$A44)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="19" t="n">
         <f aca="false">COUNTIFS(Bags!$Y$3:$Y$503,$A44,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="30" t="n">
         <f aca="false">IFERROR(C44/B44,0)</f>
@@ -39155,15 +39227,15 @@
       </c>
       <c r="E44" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$Y$3:$Y$503,$A44,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>603</v>
+        <v>964</v>
       </c>
       <c r="F44" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$Y$3:$Y$503,$A44)</f>
-        <v>201</v>
+        <v>434</v>
       </c>
       <c r="G44" s="30" t="n">
         <f aca="false">IFERROR(F44/E44,0)</f>
-        <v>0.333333333333333</v>
+        <v>0.450207468879668</v>
       </c>
       <c r="H44" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$Y$3:$Y$503,$A44,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -39171,7 +39243,7 @@
       </c>
       <c r="I44" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$Y$3:$Y$503,$A44,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>0.5</v>
+        <v>0.442727272727273</v>
       </c>
       <c r="J44" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$Y$3:$Y$503,$A44,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
@@ -39184,27 +39256,27 @@
       </c>
       <c r="B45" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$Y$3:$Y$503,$A45)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" s="19" t="n">
         <f aca="false">COUNTIFS(Bags!$Y$3:$Y$503,$A45,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45" s="30" t="n">
         <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0.625</v>
+        <v>0.857142857142857</v>
       </c>
       <c r="E45" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$Y$3:$Y$503,$A45,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>872</v>
+        <v>1040</v>
       </c>
       <c r="F45" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$Y$3:$Y$503,$A45)</f>
-        <v>729</v>
+        <v>868</v>
       </c>
       <c r="G45" s="30" t="n">
         <f aca="false">IFERROR(F45/E45,0)</f>
-        <v>0.836009174311927</v>
+        <v>0.834615384615385</v>
       </c>
       <c r="H45" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$Y$3:$Y$503,$A45,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -39212,11 +39284,11 @@
       </c>
       <c r="I45" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$Y$3:$Y$503,$A45,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>-0.762169382449249</v>
+        <v>-0.7195289810853</v>
       </c>
       <c r="J45" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$Y$3:$Y$503,$A45,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
-        <v>85</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39237,15 +39309,15 @@
       </c>
       <c r="E46" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$Y$3:$Y$503,$A46,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F46" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$Y$3:$Y$503,$A46)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G46" s="30" t="n">
         <f aca="false">IFERROR(F46/E46,0)</f>
-        <v>0.126984126984127</v>
+        <v>0.138461538461538</v>
       </c>
       <c r="H46" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$Y$3:$Y$503,$A46,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -39253,7 +39325,7 @@
       </c>
       <c r="I46" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$Y$3:$Y$503,$A46,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>0.3</v>
+        <v>0.301075268817204</v>
       </c>
       <c r="J46" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$Y$3:$Y$503,$A46,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
@@ -39262,7 +39334,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B47" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$Y$3:$Y$503,$A47)</f>
@@ -39303,7 +39375,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B48" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$Y$3:$Y$503,$A48)</f>
@@ -39344,31 +39416,31 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="B49" s="19" t="n">
         <f aca="false">COUNTIF(Bags!$Y$3:$Y$503,$A49)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" s="19" t="n">
         <f aca="false">COUNTIFS(Bags!$Y$3:$Y$503,$A49,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" s="30" t="n">
         <f aca="false">IFERROR(C49/B49,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$AE$3:$AE$503,Bags!$Y$3:$Y$503,$A49,Bags!$AC$3:$AC$503,"Sold")</f>
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="F49" s="32" t="n">
         <f aca="false">SUMIFS(Bags!$AI$3:$AI$503,Bags!$Y$3:$Y$503,$A49)</f>
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="G49" s="30" t="n">
         <f aca="false">IFERROR(F49/E49,0)</f>
-        <v>0</v>
+        <v>0.943217665615142</v>
       </c>
       <c r="H49" s="19" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AL$3:$AL$503,Bags!$Y$3:$Y$503,$A49,Bags!$AC$3:$AC$503,"Sold"),0)</f>
@@ -39376,7 +39448,7 @@
       </c>
       <c r="I49" s="30" t="n">
         <f aca="false">IFERROR(AVERAGEIFS(Bags!$AM$3:$AM$503,Bags!$Y$3:$Y$503,$A49,Bags!$AC$3:$AC$503,"Sold"),0)</f>
-        <v>0</v>
+        <v>0.630536130536131</v>
       </c>
       <c r="J49" s="31" t="n">
         <f aca="false">SUMIFS(Bags!$X$3:$X$503,Bags!$Y$3:$Y$503,$A49,Bags!$AC$3:$AC$503,"&lt;&gt;Sold")</f>
@@ -39416,7 +39488,7 @@
         <v>35</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>50</v>
@@ -39425,7 +39497,7 @@
         <v>54</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>37</v>
@@ -39436,10 +39508,10 @@
         <v>132</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>77</v>
@@ -39448,7 +39520,7 @@
         <v>78</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>80</v>
@@ -39462,39 +39534,39 @@
         <v>83</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>86</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>104</v>
@@ -39503,7 +39575,7 @@
         <v>79</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39514,16 +39586,16 @@
         <v>96</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>101</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39534,35 +39606,35 @@
         <v>85</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39577,37 +39649,37 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
